--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:23:29+00:00</t>
+    <t>2023-12-18T12:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:24:31+00:00</t>
+    <t>2023-12-18T13:29:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T13:29:44+00:00</t>
+    <t>2023-12-19T08:36:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-2</t>
+    <t>1.0.0-ballot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T08:36:38+00:00</t>
+    <t>2023-12-19T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T15:11:46+00:00</t>
+    <t>2023-12-21T16:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:59:47+00:00</t>
+    <t>2024-01-11T15:09:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T15:09:13+00:00</t>
+    <t>2024-02-05T18:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:24+00:00</t>
+    <t>2024-02-05T18:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:48+00:00</t>
+    <t>2024-02-05T18:23:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:23:38+00:00</t>
+    <t>2024-02-07T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T08:22:38+00:00</t>
+    <t>2024-02-08T15:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:43:07+00:00</t>
+    <t>2024-02-08T15:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:45:12+00:00</t>
+    <t>2024-02-16T10:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:46:50+00:00</t>
+    <t>2024-02-16T10:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-education-level.xlsx
+++ b/ig/main/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:57:00+00:00</t>
+    <t>2024-02-16T18:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
